--- a/data/daily/2026-09/2026-09-21.xlsx
+++ b/data/daily/2026-09/2026-09-21.xlsx
@@ -1195,7 +1195,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="323850" cy="457200"/>
+    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1270,14 +1270,39 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,35 +1342,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="361950" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1450,7 +1450,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
+    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1525,27 +1525,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1553,54 +1578,29 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="990600" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 고급스러운 패키지와 구성으로 지인 선물용 호불호 없이 적합함</t>
+          <t>선물에 적합한 패키지 — 패키지가 고급스럽고 카카오톡으로 가볍게 선물하기에 적합함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>우수한 휴대성 및 편의성 — 한 병씩 가방에 쏙 넣어 다니기 간편하고 맛이 좋음</t>
+          <t>뛰어난 피로 회복 체감 — 지친 피로를 풀어주고 빠른 컨디션 회복 및 에너지 충전에 도움이 됨</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 피곤함을 달래고 에너지를 충전하여 단기간 컨디션 올리기에 좋음</t>
+          <t>간편한 휴대성과 우수한 맛 — 한 병씩 들고 다니기 편하며 맛이 좋아 부담 없이 복용 가능함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2659,17 +2659,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>편리한 섭취 및 휴대성 — 한 병에 알약과 맛있는 액상이 함께 들어 있어 휴대와 섭취가 편함</t>
+          <t>빠른 배송과 깔끔한 포장 — 배송이 빠르고 선물 패키지 포장이 깔끔하여 매우 만족스러움</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>활력 충전 및 피로 개선 — 섭취 후 피로감이 줄어들고 활력과 컨디션이 좋아짐</t>
+          <t>우수한 활력 증진 효과 — 섭취 후 피로가 줄어들고 일상 활력이 도는 것을 체감함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>깔끔한 포장과 빠른 배송 — 선물 패키지 포장이 깔끔하고 배송이 빠르게 완료됨</t>
+          <t>휴대와 섭취의 간편성 — 한 병에 정제와 액상이 같이 들어 있어 들고 다니며 먹기 편리함</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2718,18 +2718,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>체력 증진 및 피로 회복 — 섭취 후 덜 피곤하고 기력 및 컨디션 유지에 에너지를 얻음</t>
+          <t>확실한 피로 개선 체감 — 체력 및 기력 보충에 우수하며 피로감이 줄어드는 것을 체감함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 명절 기프트 에디션 케이스가 예쁘고 고급스러워 선물용으로 훌륭함</t>
+          <t>고급스러운 선물 케이스 — 패키지 케이스가 예쁘고 고급스러워 명절 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>구매 직후 가격 인하 — 제품 구매 후 가격이 추가 할인되어 아쉬움이 남음</t>
+          <t>구매 직후 가격 인하 — 제품 구매 직후 가격이 할인되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2773,26 +2773,22 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>8711</v>
+        <v>8712</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 체감 — 섭취 후 피로감이 줄어들고 반짝이듯 빠르게 생기가 도는 느낌을 받음</t>
+          <t>강력한 피로 개선 효과 — 섭취 후 피로감이 확 줄어들고 강한 에너지를 체감함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 증정 구성 — 추가 증정 서비스 구성과 무난한 가격대 대비 가성비가 훌륭함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>우수한 휴대성과 선물 만족도 — 포장이 예쁘고 휴대하기 간편하여 마음을 전달하는 선물로 적합함</t>
-        </is>
-      </c>
+          <t>예쁜 포장과 편리한 휴대 — 포장이 예쁘고 휴대성이 좋아 가볍게 챙겨 먹기 적합함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>섭취 후 소변 색 변화 — 비타민 성분으로 인해 섭취 후 하루 종일 소변 색이 진하게 변함</t>
+          <t>평범하고 무난한 제품 — 제품 자체는 가성비가 좋으나 무난한 느낌을 줌</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2809,55 +2805,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>43,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/11866425</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260831093017_c95c591e7b5b4e3d9e549888b299930a.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>760</v>
+        <v>788</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>피로 회복 및 컨디션 개선 — 필수 영양소 보충으로 당일 컨디션 상승과 피로 회복에 효과적임</t>
+          <t>신속한 컨디션 회복 — 섭취 후 피로가 해소되고 컨디션이 빠르게 회복됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>알찬 구성과 합리적 가격 — 부담 없는 가격과 넉넉한 구성으로 재구매 의사가 큼</t>
+          <t>작은 정제 크기와 편의성 — 정제 크기가 작아 삼키기 쉽고 한 번에 영양을 챙기기 편함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>간편한 휴대성과 깔끔한 포장 — 휴대와 섭취가 편하며 깔끔한 패키지 포장으로 명절 선물용에 적합함</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>명절 기간 배송 지연 — 추석 연휴 물량 증가로 인해 배송에 다소 시간이 소요됨</t>
-        </is>
-      </c>
+          <t>고급스러운 선물용 포장 — 포장이 고급스럽게 잘 되어 있어 생일 선물로 적합함</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -2872,48 +2864,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>43,000원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11866425</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260831093017_c95c591e7b5b4e3d9e549888b299930a.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>788</v>
+        <v>761</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>한 번에 챙기는 편의성 — 알약 크기가 크지 않고 멀티비타민을 한 번에 챙길 수 있어 편함</t>
+          <t>합리적인 가격과 구성 — 가격 대비 영양소 구성이 알차고 만족스러움</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>확실한 체력 증진 효과 — 피로가 누적된 일상에서 하나만 먹어도 체력 회복에 도움을 받음</t>
+          <t>우수한 피로 회복 체감 — 섭취 후 컨디션이 좋아지고 활력 증진에 도움 됨</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 포장이 깔끔하고 고급스러워 생일이나 기념일 선물용으로 적합함</t>
+          <t>빠른 배송과 깔끔한 포장 — 배송이 빠르고 패키지가 깔끔하여 명절 선물용으로 우수함</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -2962,17 +2954,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>맛있는 젤리형 복용 편의성 — 물 없이 간편하게 씹어 먹을 수 있고 맛이 좋아 매일 챙겨 먹기 편함</t>
+          <t>맛있는 구미 젤리 제형 — 맛있는 젤리 형태라 거부감 없이 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>귀엽고 깔끔한 패키지 — 귀여운 포장 디자인과 키캡 사은품 구성으로 가볍게 선물하기 좋음</t>
+          <t>물 없이 섭취 가능한 편의성 — 물이 필요 없어 어디서나 간편하게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>부담 없는 온가족 섭취 — 연령대 상관없이 부담 없이 맛있게 먹을 수 있음</t>
+          <t>귀엽고 깔끔한 패키지 — 포장이 귀엽고 깔끔하여 가볍게 선물하기 적합함</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3017,26 +3009,26 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>명확한 피로 회복 효과 — 복용한 날과 안 먹은 날의 차이가 체감될 정도로 에너지가 생김</t>
+          <t>체감되는 에너지 보충 — 복용 여부에 따른 차이가 분명하고 활력이 잘 돎</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 투명한 케이스와 정성스러운 포장으로 선물 전달용으로 우수함</t>
+          <t>고급 투명 케이스 디자인 — 투명한 용기 패키지가 고급스러우며 명절 선물로 적합함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>새콤달콤한 맛과 쉬운 음용 — 새콤달콤한 오렌지 맛으로 맛있고 음용법이 간단함</t>
+          <t>물 없이 편한 섭취와 맛 — 맛이 좋고 물 없이 간편하게 마시기 편리함</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>분말 뚜껑 개봉의 불편함 — 분말 뚜껑을 열 때 세게 눌러야 하는 약간의 불편함이 존재함</t>
+          <t>분말 뚜껑 개봉의 뻑뻑함 — 분말 뚜껑 부분을 다소 세게 눌러야 개봉됨</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -3084,22 +3076,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>성별 맞춤형 영양 설계 — 남성용과 여성용을 선택할 수 있어 맞춤 영양 관리가 가능함</t>
+          <t>성별 맞춤형 영양 구성 — 성별 선택이 가능하며 풍부한 영양 성분을 갖춤</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>지속적인 활력 유지를 도움 — 꾸준히 섭취 시 반짝이는 기분과 활력이 오랫동안 유지됨</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>정성스러운 선물용 포장 — 포장이 깔끔하고 정성스러워 생일 선물용 만족도가 높음</t>
-        </is>
-      </c>
+          <t>지속적인 피로 개선 — 꾸준히 복용 시 활력이 오래 유지되고 피로도가 낮아짐</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼킬 때 약간 부담스러움</t>
+          <t>다소 큰 정제 크기 — 알약의 크기가 다소 크다 보니 목넘김에 부담이 있음</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3143,21 +3131,21 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>29581</v>
+        <v>29588</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>쉬운 캡 개봉과 부드러운 목넘김 — 뚜껑 개봉이 편리하고 액상이 묽어 알약과 함께 삼키기 쉬움</t>
+          <t>올인원 일체형 섭취 — 액상, 정제, 캡슐이 한 병에 포함되어 챙기기 간편함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 섭취 후 피로가 빠르게 풀리고 기상 시 몸이 가벼워지는 것을 체감함</t>
+          <t>고급 소나무 패키지 — 쇼핑백과 고급 소나무 일러스트 패키지로 명절 선물에 적합함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>합리적인 가격과 고급 포장 — 가격이 합리적이면서 고급스러운 포장으로 호불호 없는 선물로 좋음</t>
+          <t>맛있는 비타민과 젤리 — 맛이 좋고 증정품으로 제공되는 젤리도 상큼함</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -3206,22 +3194,18 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>고급스러운 보자기 포장 — 틴케이스와 보자기, 쇼핑백 등 선물 포장이 매우 고급스럽고 예쁨</t>
+          <t>고급스러운 오간자 포장 — 틴케이스와 보자기 등 고급스럽고 예쁜 선물 포장을 제공함</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>비리지 않은 맛있는 앰플 — 비린 맛 없이 맛있으며 낱개 앰플 형태로 하루 하나씩 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>높은 선물 만족도 — 예쁜 용기와 정성스러운 디자인으로 받는 사람의 기분을 좋게 함</t>
-        </is>
-      </c>
+          <t>비린 맛 없는 개별 앰플 — 콜라겐 비린 맛이 없고 낱개 앰플 형태라 섭취가 쉬움</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>지속적인 가격 상승 부담 — 할인 혜택이 좋으나 원제품 가격이 점차 올라 가격 부담이 존재함</t>
+          <t>지속적인 가격 상승 — 시간이 지날수록 판매 가격이 오르는 점이 아쉬움</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3269,22 +3253,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>부드러운 식감과 다양한 맛 — 뻑뻑함이 적고 맛이 다채로워 매일 먹어도 질리지 않음</t>
+          <t>부드러운 식감과 다양한 맛 — 퍽퍽하지 않고 부드러우며 맛 종류가 다양해 질리지 않음</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>우수한 가성비 및 포장 — 수량 대비 가격이 저렴하며 포장 상태와 배송이 꼼꼼함</t>
+          <t>뛰어난 가성비 구성 — 많은 양의 닭가슴살을 저렴하게 구매할 수 있어 경제적임</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>간편한 전자레인지 조리 — 전자레인지로 조리가 가능하여 간편하게 다이어트 식단을 챙김</t>
+          <t>간편한 조리 방식 — 전자레인지 조리로 간편하게 식단 관리가 가능함</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>배송 중 제품 융해 발생 — 배송 과정에서 제품이 녹아서 도착하는 경우가 발생함</t>
+          <t>배송 중 해동 발생 — 배송 과정에서 제품이 완전히 녹아 도착하는 문제가 있음</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3301,7 +3285,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3311,43 +3295,43 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260921093919_9881af9e82944da586785c0fe2e5715a.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>1677</v>
+        <v>883</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>소화 촉진 및 속 편안함 — 식후 복용 시 소화가 잘 되고 속이 편안해지며 배변에 도움을 줌</t>
+          <t>물 없이 섭취하는 편리함 — 물 없이도 복용할 수 있어 언제 어디서나 먹기 편함</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>고소하고 부담 없는 맛 — 맛이 고소하여 거부감 없이 편안하게 복용할 수 있음</t>
+          <t>속 편안한 소화 개선 — 식후 복용 시 속이 편안해지고 소화 촉진 및 배변에 도움 됨</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>풍성한 방송 특가 혜택 — 라이브 방송 구매 시 가격 조건이 좋고 사은품 혜택이 큼</t>
+          <t>합리적인 가격과 맛 — 가격대가 좋고 맛도 뛰어나 부담 없이 먹을 수 있음</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>사은품의 작은 용량 — 증정품으로 제공된 단백질 칩의 크기가 매우 작음</t>
+          <t>기존 제품 대비 맛 차이 — 이전에 복용하던 카무트 효소 제품과 맛에 차이가 존재함</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3364,7 +3348,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3374,39 +3358,43 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260921093919_9881af9e82944da586785c0fe2e5715a.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>883</v>
+        <v>1677</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>물 없이 먹는 높은 편의성 — 물 없이도 편하게 먹을 수 있어 언제 어디서나 섭취 가능함</t>
+          <t>우수한 소화 및 배변 개선 — 소화 촉진과 변비 해소에 효과적이며 속이 편해짐</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 식후 섭취 시 소화가 잘 되고 아침 배변 활동이 원활해짐</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>고소하고 완만한 풍미 — 고소한 맛으로 거부감 없이 편하게 섭취할 수 있음</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>고급 포장과 방송 혜택 — 선물 포장이 고급스럽고 라이브 방송 혜택 및 사은품이 풍부함</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>기존 제품과의 맛 차이 — 기존에 복용하던 일반 카무트 제품과 맛에 다소 차이가 존재함</t>
+          <t>사은품 단백질 칩의 크기 — 증정품으로 함께 제공된 단백질 칩의 크기가 다소 작음</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3450,25 +3438,29 @@
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>다채로운 맛과 구성 — 여러 맛으로 구성되어 질리지 않고 맛있게 식단을 관리할 수 있음</t>
+          <t>다양한 골라 먹는 구성 — 다양한 종류의 맛으로 구성되어 매일 바꿔 먹기 좋음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>훌륭한 가성비와 보냉백 증정 — 저렴한 가격에 풍성한 수량과 실용적인 보냉 파우치를 함께 증정함</t>
+          <t>합리적인 가격과 양 — 한 달 식단으로 가격 대비 제품 수량이 풍부함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>일부 제품의 포장 불량 — 진공 포장이 헐렁하거나 팩이 터져 소스가 묻어 나오는 배송 불량이 있음</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>제품 오배송 및 대응 미흡 — 신청한 구성과 다르게 제품이 중복 오배송되고 문의 대응이 늦음</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>포장 불량 및 소스 누출 — 진공 포장이 헐렁하거나 팩이 터져 소스가 셀 수 있음</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
@@ -3513,23 +3505,23 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>고소하고 맛있는 베리말차맛 — 효소 특유의 맛 대신 고소하고 맛있게 섭취할 수 있음</t>
+          <t>맛있는 베리말차 효소 — 고소하고 달콤하여 효소임에도 기대 이상으로 맛있음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>알찬 사은품 혜택 구성 — 단백질바와 사진 포토카드가 함께 동봉되어 만족도가 높음</t>
+          <t>알찬 굿즈 및 사은품 — 단백질바 사은품과 리센느 원이 포토카드가 만족스러움</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>다소 느린 배송 속도 — 타 구매처 대비 배송 일정이 약간 늦게 진행됨</t>
+          <t>다소 아쉬운 배송 속도 — 주문 후 제품 배송까지의 시간이 다소 걸리는 편임</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>포토카드 고정 지급 아쉬움 — 포토카드가 랜덤 지급이 아닌 고정 디자인으로 제공됨</t>
+          <t>포토카드 고정 지급 — 동봉된 포토카드가 랜덤이 아닌 고정형이라 다소 아쉬움</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -3576,18 +3568,18 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>예쁘고 고급스러운 패키지 — 포장 케이스와 병 디자인이 매우 예쁘고 고급스러워 선물용으로 좋음</t>
+          <t>공주풍 디자인 포장 — 용기와 패키지 디자인이 예쁘고 고급스러워 기분 좋음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>거부감 없는 맛있는 앰플 — 약 맛 대신 맛있는 음료 느낌으로 먹을 수 있어 섭취가 간편함</t>
+          <t>상큼하고 맛있는 맛 — 약 맛이 아닌 상큼한 맛으로 거부감 없이 복용 가능함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>단기 섭취 시 효과 체감 미흡 — 짧은 복용 기간 기준으로는 즉각적인 효과 체감이 다소 부족함</t>
+          <t>진한 제형 농도 — 액상 농도가 조금 진하여 복용 후 물을 마시게 됨</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -3635,17 +3627,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>비린 맛 없는 달콤한 맛 — 단백질 음료 특유의 비리고 텁텁한 맛이 없이 진한 초코우유 같음</t>
+          <t>비린 맛 없는 달콤함 — 단백질 음료 특유의 비리고 텁텁한 맛이 없으며 달콤함</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>부드러운 목넘김과 속 편함 — 목넘김이 부드럽고 마신 뒤 속 더부룩함이나 텁텁함이 적음</t>
+          <t>속 편안한 포만감 제공 — 마신 뒤 속 더부룩함이 없고 은근한 포만감을 제공함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>슬림한 용기의 높은 휴대성 — 패키지가 슬림하여 가방에 넣어 다니며 운동 후 간편하게 챙김</t>
+          <t>휴대하기 편한 패키지 — 용기 디자인이 슬림하여 가방에 넣어 휴대하기에 편리함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3694,17 +3686,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>확실한 활력 및 체력 증진 — 6,200mg 고함량으로 운동 수행 능력과 피로 회복에 효과적임</t>
+          <t>체감되는 확실한 활력 — 6200mg 고함량으로 섭취 후 피로 감소와 활력 증진을 느낌</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>개별 포장의 높은 휴대성 — 스틱 형태로 개별 포장되어 있어 가지고 다니며 하루 1포 먹기 편함</t>
+          <t>1포 개별 포장 간편성 — 하루 1포 개별 스틱 포장으로 휴대가 편하고 복용이 쉬움</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 구성 — 쇼핑백과 추가 포 증정 구성으로 고급스러운 선물감이 돋보임</t>
+          <t>고급스러운 선물 패키지 — 블랙과 레드 디자인의 패키지와 전용 쇼핑백 증정이 훌륭함</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3753,17 +3745,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 충전 — 아침 기상 시 몸이 가벼워지고 일상 및 운동 중 피로 회복 효과가 큼</t>
+          <t>아침 피로 완화와 활력 — 아침 일어남이 가볍고 운동 시 피로감이 줄어듦</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>알찬 이중 영양제 구성 — 아르기닌과 밀크씨슬을 한 번에 챙길 수 있는 2개월분 구성이라 유용함</t>
+          <t>알찬 2개월 세트 구성 — 간 건강과 활력을 한 번에 챙기는 넉넉한 2개월분 세트임</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>쇼핑백 증정으로 선물 적합 — 전용 쇼핑백이 함께 증정되어 활력 선물용으로 전달하기 좋음</t>
+          <t>선물하기 좋은 쇼핑백 증정 — 쇼핑백이 함께 포함되어 선물용으로 건네기에 적합함</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3958,12 +3950,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -4015,12 +4007,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4097,25 +4089,25 @@
         <v>3358</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>8711</v>
+        <v>8712</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>760</v>
+        <v>788</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>788</v>
+        <v>761</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>6483</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>771</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>29581</v>
+        <v>29588</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -4126,71 +4118,69 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 고급스러운 패키지와 구성으로 지인 선물용 호불호 없이 적합함
-우수한 휴대성 및 편의성 — 한 병씩 가방에 쏙 넣어 다니기 간편하고 맛이 좋음
-확실한 피로 회복 효과 — 피곤함을 달래고 에너지를 충전하여 단기간 컨디션 올리기에 좋음</t>
+          <t>선물에 적합한 패키지 — 패키지가 고급스럽고 카카오톡으로 가볍게 선물하기에 적합함
+뛰어난 피로 회복 체감 — 지친 피로를 풀어주고 빠른 컨디션 회복 및 에너지 충전에 도움이 됨
+간편한 휴대성과 우수한 맛 — 한 병씩 들고 다니기 편하며 맛이 좋아 부담 없이 복용 가능함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>편리한 섭취 및 휴대성 — 한 병에 알약과 맛있는 액상이 함께 들어 있어 휴대와 섭취가 편함
-활력 충전 및 피로 개선 — 섭취 후 피로감이 줄어들고 활력과 컨디션이 좋아짐
-깔끔한 포장과 빠른 배송 — 선물 패키지 포장이 깔끔하고 배송이 빠르게 완료됨</t>
+          <t>빠른 배송과 깔끔한 포장 — 배송이 빠르고 선물 패키지 포장이 깔끔하여 매우 만족스러움
+우수한 활력 증진 효과 — 섭취 후 피로가 줄어들고 일상 활력이 도는 것을 체감함
+휴대와 섭취의 간편성 — 한 병에 정제와 액상이 같이 들어 있어 들고 다니며 먹기 편리함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>체력 증진 및 피로 회복 — 섭취 후 덜 피곤하고 기력 및 컨디션 유지에 에너지를 얻음
-고급스러운 패키지 디자인 — 명절 기프트 에디션 케이스가 예쁘고 고급스러워 선물용으로 훌륭함</t>
+          <t>확실한 피로 개선 체감 — 체력 및 기력 보충에 우수하며 피로감이 줄어드는 것을 체감함
+고급스러운 선물 케이스 — 패키지 케이스가 예쁘고 고급스러워 명절 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 체감 — 섭취 후 피로감이 줄어들고 반짝이듯 빠르게 생기가 도는 느낌을 받음
-뛰어난 가성비와 증정 구성 — 추가 증정 서비스 구성과 무난한 가격대 대비 가성비가 훌륭함
-우수한 휴대성과 선물 만족도 — 포장이 예쁘고 휴대하기 간편하여 마음을 전달하는 선물로 적합함</t>
+          <t>강력한 피로 개선 효과 — 섭취 후 피로감이 확 줄어들고 강한 에너지를 체감함
+예쁜 포장과 편리한 휴대 — 포장이 예쁘고 휴대성이 좋아 가볍게 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 컨디션 개선 — 필수 영양소 보충으로 당일 컨디션 상승과 피로 회복에 효과적임
-알찬 구성과 합리적 가격 — 부담 없는 가격과 넉넉한 구성으로 재구매 의사가 큼
-간편한 휴대성과 깔끔한 포장 — 휴대와 섭취가 편하며 깔끔한 패키지 포장으로 명절 선물용에 적합함</t>
+          <t>신속한 컨디션 회복 — 섭취 후 피로가 해소되고 컨디션이 빠르게 회복됨
+작은 정제 크기와 편의성 — 정제 크기가 작아 삼키기 쉽고 한 번에 영양을 챙기기 편함
+고급스러운 선물용 포장 — 포장이 고급스럽게 잘 되어 있어 생일 선물로 적합함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>한 번에 챙기는 편의성 — 알약 크기가 크지 않고 멀티비타민을 한 번에 챙길 수 있어 편함
-확실한 체력 증진 효과 — 피로가 누적된 일상에서 하나만 먹어도 체력 회복에 도움을 받음
-고급스러운 선물 포장 — 포장이 깔끔하고 고급스러워 생일이나 기념일 선물용으로 적합함</t>
+          <t>합리적인 가격과 구성 — 가격 대비 영양소 구성이 알차고 만족스러움
+우수한 피로 회복 체감 — 섭취 후 컨디션이 좋아지고 활력 증진에 도움 됨
+빠른 배송과 깔끔한 포장 — 배송이 빠르고 패키지가 깔끔하여 명절 선물용으로 우수함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리형 복용 편의성 — 물 없이 간편하게 씹어 먹을 수 있고 맛이 좋아 매일 챙겨 먹기 편함
-귀엽고 깔끔한 패키지 — 귀여운 포장 디자인과 키캡 사은품 구성으로 가볍게 선물하기 좋음
-부담 없는 온가족 섭취 — 연령대 상관없이 부담 없이 맛있게 먹을 수 있음</t>
+          <t>맛있는 구미 젤리 제형 — 맛있는 젤리 형태라 거부감 없이 맛있게 먹을 수 있음
+물 없이 섭취 가능한 편의성 — 물이 필요 없어 어디서나 간편하게 챙겨 먹기 좋음
+귀엽고 깔끔한 패키지 — 포장이 귀엽고 깔끔하여 가볍게 선물하기 적합함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>명확한 피로 회복 효과 — 복용한 날과 안 먹은 날의 차이가 체감될 정도로 에너지가 생김
-고급스러운 패키지 디자인 — 투명한 케이스와 정성스러운 포장으로 선물 전달용으로 우수함
-새콤달콤한 맛과 쉬운 음용 — 새콤달콤한 오렌지 맛으로 맛있고 음용법이 간단함</t>
+          <t>체감되는 에너지 보충 — 복용 여부에 따른 차이가 분명하고 활력이 잘 돎
+고급 투명 케이스 디자인 — 투명한 용기 패키지가 고급스러우며 명절 선물로 적합함
+물 없이 편한 섭취와 맛 — 맛이 좋고 물 없이 간편하게 마시기 편리함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤형 영양 설계 — 남성용과 여성용을 선택할 수 있어 맞춤 영양 관리가 가능함
-지속적인 활력 유지를 도움 — 꾸준히 섭취 시 반짝이는 기분과 활력이 오랫동안 유지됨
-정성스러운 선물용 포장 — 포장이 깔끔하고 정성스러워 생일 선물용 만족도가 높음</t>
+          <t>성별 맞춤형 영양 구성 — 성별 선택이 가능하며 풍부한 영양 성분을 갖춤
+지속적인 피로 개선 — 꾸준히 복용 시 활력이 오래 유지되고 피로도가 낮아짐</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>쉬운 캡 개봉과 부드러운 목넘김 — 뚜껑 개봉이 편리하고 액상이 묽어 알약과 함께 삼키기 쉬움
-뛰어난 피로 회복 효과 — 섭취 후 피로가 빠르게 풀리고 기상 시 몸이 가벼워지는 것을 체감함
-합리적인 가격과 고급 포장 — 가격이 합리적이면서 고급스러운 포장으로 호불호 없는 선물로 좋음</t>
+          <t>올인원 일체형 섭취 — 액상, 정제, 캡슐이 한 병에 포함되어 챙기기 간편함
+고급 소나무 패키지 — 쇼핑백과 고급 소나무 일러스트 패키지로 명절 선물에 적합함
+맛있는 비타민과 젤리 — 맛이 좋고 증정품으로 제공되는 젤리도 상큼함</t>
         </is>
       </c>
     </row>
@@ -4204,29 +4194,25 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>구매 직후 가격 인하 — 제품 구매 후 가격이 추가 할인되어 아쉬움이 남음</t>
+          <t>구매 직후 가격 인하 — 제품 구매 직후 가격이 할인되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>섭취 후 소변 색 변화 — 비타민 성분으로 인해 섭취 후 하루 종일 소변 색이 진하게 변함</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>명절 기간 배송 지연 — 추석 연휴 물량 증가로 인해 배송에 다소 시간이 소요됨</t>
-        </is>
-      </c>
+          <t>평범하고 무난한 제품 — 제품 자체는 가성비가 좋으나 무난한 느낌을 줌</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>분말 뚜껑 개봉의 불편함 — 분말 뚜껑을 열 때 세게 눌러야 하는 약간의 불편함이 존재함</t>
+          <t>분말 뚜껑 개봉의 뻑뻑함 — 분말 뚜껑 부분을 다소 세게 눌러야 개봉됨</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼킬 때 약간 부담스러움</t>
+          <t>다소 큰 정제 크기 — 알약의 크기가 다소 크다 보니 목넘김에 부담이 있음</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -4259,12 +4245,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>43,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>52,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>43,000원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -4551,12 +4537,12 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -4640,13 +4626,13 @@
         <v>52</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>883</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>1677</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>883</v>
-      </c>
       <c r="G19" s="3" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>95</v>
@@ -4672,68 +4658,68 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 보자기 포장 — 틴케이스와 보자기, 쇼핑백 등 선물 포장이 매우 고급스럽고 예쁨
-비리지 않은 맛있는 앰플 — 비린 맛 없이 맛있으며 낱개 앰플 형태로 하루 하나씩 먹기 편함
-높은 선물 만족도 — 예쁜 용기와 정성스러운 디자인으로 받는 사람의 기분을 좋게 함</t>
+          <t>고급스러운 오간자 포장 — 틴케이스와 보자기 등 고급스럽고 예쁜 선물 포장을 제공함
+비린 맛 없는 개별 앰플 — 콜라겐 비린 맛이 없고 낱개 앰플 형태라 섭취가 쉬움</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>부드러운 식감과 다양한 맛 — 뻑뻑함이 적고 맛이 다채로워 매일 먹어도 질리지 않음
-우수한 가성비 및 포장 — 수량 대비 가격이 저렴하며 포장 상태와 배송이 꼼꼼함
-간편한 전자레인지 조리 — 전자레인지로 조리가 가능하여 간편하게 다이어트 식단을 챙김</t>
+          <t>부드러운 식감과 다양한 맛 — 퍽퍽하지 않고 부드러우며 맛 종류가 다양해 질리지 않음
+뛰어난 가성비 구성 — 많은 양의 닭가슴살을 저렴하게 구매할 수 있어 경제적임
+간편한 조리 방식 — 전자레인지 조리로 간편하게 식단 관리가 가능함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>소화 촉진 및 속 편안함 — 식후 복용 시 소화가 잘 되고 속이 편안해지며 배변에 도움을 줌
-고소하고 부담 없는 맛 — 맛이 고소하여 거부감 없이 편안하게 복용할 수 있음
-풍성한 방송 특가 혜택 — 라이브 방송 구매 시 가격 조건이 좋고 사은품 혜택이 큼</t>
+          <t>물 없이 섭취하는 편리함 — 물 없이도 복용할 수 있어 언제 어디서나 먹기 편함
+속 편안한 소화 개선 — 식후 복용 시 속이 편안해지고 소화 촉진 및 배변에 도움 됨
+합리적인 가격과 맛 — 가격대가 좋고 맛도 뛰어나 부담 없이 먹을 수 있음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>물 없이 먹는 높은 편의성 — 물 없이도 편하게 먹을 수 있어 언제 어디서나 섭취 가능함
-속 편한 소화 개선 효과 — 식후 섭취 시 소화가 잘 되고 아침 배변 활동이 원활해짐</t>
+          <t>우수한 소화 및 배변 개선 — 소화 촉진과 변비 해소에 효과적이며 속이 편해짐
+고소하고 완만한 풍미 — 고소한 맛으로 거부감 없이 편하게 섭취할 수 있음
+고급 포장과 방송 혜택 — 선물 포장이 고급스럽고 라이브 방송 혜택 및 사은품이 풍부함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>다채로운 맛과 구성 — 여러 맛으로 구성되어 질리지 않고 맛있게 식단을 관리할 수 있음
-훌륭한 가성비와 보냉백 증정 — 저렴한 가격에 풍성한 수량과 실용적인 보냉 파우치를 함께 증정함</t>
+          <t>다양한 골라 먹는 구성 — 다양한 종류의 맛으로 구성되어 매일 바꿔 먹기 좋음
+합리적인 가격과 양 — 한 달 식단으로 가격 대비 제품 수량이 풍부함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>고소하고 맛있는 베리말차맛 — 효소 특유의 맛 대신 고소하고 맛있게 섭취할 수 있음
-알찬 사은품 혜택 구성 — 단백질바와 사진 포토카드가 함께 동봉되어 만족도가 높음</t>
+          <t>맛있는 베리말차 효소 — 고소하고 달콤하여 효소임에도 기대 이상으로 맛있음
+알찬 굿즈 및 사은품 — 단백질바 사은품과 리센느 원이 포토카드가 만족스러움</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>예쁘고 고급스러운 패키지 — 포장 케이스와 병 디자인이 매우 예쁘고 고급스러워 선물용으로 좋음
-거부감 없는 맛있는 앰플 — 약 맛 대신 맛있는 음료 느낌으로 먹을 수 있어 섭취가 간편함</t>
+          <t>공주풍 디자인 포장 — 용기와 패키지 디자인이 예쁘고 고급스러워 기분 좋음
+상큼하고 맛있는 맛 — 약 맛이 아닌 상큼한 맛으로 거부감 없이 복용 가능함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 달콤한 맛 — 단백질 음료 특유의 비리고 텁텁한 맛이 없이 진한 초코우유 같음
-부드러운 목넘김과 속 편함 — 목넘김이 부드럽고 마신 뒤 속 더부룩함이나 텁텁함이 적음
-슬림한 용기의 높은 휴대성 — 패키지가 슬림하여 가방에 넣어 다니며 운동 후 간편하게 챙김</t>
+          <t>비린 맛 없는 달콤함 — 단백질 음료 특유의 비리고 텁텁한 맛이 없으며 달콤함
+속 편안한 포만감 제공 — 마신 뒤 속 더부룩함이 없고 은근한 포만감을 제공함
+휴대하기 편한 패키지 — 용기 디자인이 슬림하여 가방에 넣어 휴대하기에 편리함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>확실한 활력 및 체력 증진 — 6,200mg 고함량으로 운동 수행 능력과 피로 회복에 효과적임
-개별 포장의 높은 휴대성 — 스틱 형태로 개별 포장되어 있어 가지고 다니며 하루 1포 먹기 편함
-고급스러운 선물용 구성 — 쇼핑백과 추가 포 증정 구성으로 고급스러운 선물감이 돋보임</t>
+          <t>체감되는 확실한 활력 — 6200mg 고함량으로 섭취 후 피로 감소와 활력 증진을 느낌
+1포 개별 포장 간편성 — 하루 1포 개별 스틱 포장으로 휴대가 편하고 복용이 쉬움
+고급스러운 선물 패키지 — 블랙과 레드 디자인의 패키지와 전용 쇼핑백 증정이 훌륭함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 충전 — 아침 기상 시 몸이 가벼워지고 일상 및 운동 중 피로 회복 효과가 큼
-알찬 이중 영양제 구성 — 아르기닌과 밀크씨슬을 한 번에 챙길 수 있는 2개월분 구성이라 유용함
-쇼핑백 증정으로 선물 적합 — 전용 쇼핑백이 함께 증정되어 활력 선물용으로 전달하기 좋음</t>
+          <t>아침 피로 완화와 활력 — 아침 일어남이 가볍고 운동 시 피로감이 줄어듦
+알찬 2개월 세트 구성 — 간 건강과 활력을 한 번에 챙기는 넉넉한 2개월분 세트임
+선물하기 좋은 쇼핑백 증정 — 쇼핑백이 함께 포함되어 선물용으로 건네기에 적합함</t>
         </is>
       </c>
     </row>
@@ -4745,38 +4731,39 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>지속적인 가격 상승 부담 — 할인 혜택이 좋으나 원제품 가격이 점차 올라 가격 부담이 존재함</t>
+          <t>지속적인 가격 상승 — 시간이 지날수록 판매 가격이 오르는 점이 아쉬움</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 제품 융해 발생 — 배송 과정에서 제품이 녹아서 도착하는 경우가 발생함</t>
+          <t>배송 중 해동 발생 — 배송 과정에서 제품이 완전히 녹아 도착하는 문제가 있음</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>사은품의 작은 용량 — 증정품으로 제공된 단백질 칩의 크기가 매우 작음</t>
+          <t>기존 제품 대비 맛 차이 — 이전에 복용하던 카무트 효소 제품과 맛에 차이가 존재함</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>기존 제품과의 맛 차이 — 기존에 복용하던 일반 카무트 제품과 맛에 다소 차이가 존재함</t>
+          <t>사은품 단백질 칩의 크기 — 증정품으로 함께 제공된 단백질 칩의 크기가 다소 작음</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>일부 제품의 포장 불량 — 진공 포장이 헐렁하거나 팩이 터져 소스가 묻어 나오는 배송 불량이 있음</t>
+          <t>제품 오배송 및 대응 미흡 — 신청한 구성과 다르게 제품이 중복 오배송되고 문의 대응이 늦음
+포장 불량 및 소스 누출 — 진공 포장이 헐렁하거나 팩이 터져 소스가 셀 수 있음</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>다소 느린 배송 속도 — 타 구매처 대비 배송 일정이 약간 늦게 진행됨
-포토카드 고정 지급 아쉬움 — 포토카드가 랜덤 지급이 아닌 고정 디자인으로 제공됨</t>
+          <t>다소 아쉬운 배송 속도 — 주문 후 제품 배송까지의 시간이 다소 걸리는 편임
+포토카드 고정 지급 — 동봉된 포토카드가 랜덤이 아닌 고정형이라 다소 아쉬움</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>단기 섭취 시 효과 체감 미흡 — 짧은 복용 기간 기준으로는 즉각적인 효과 체감이 다소 부족함</t>
+          <t>진한 제형 농도 — 액상 농도가 조금 진하여 복용 후 물을 마시게 됨</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
@@ -4801,12 +4788,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>46,900원</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>24,900원</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -5034,45 +5021,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910891&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/tgDz0oHoOLB3gj3BLgFd610910891_00_01tgDz0oHoOLB3gj3BLgFd.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2184</v>
+        <v>2685</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>맛있고 재미있는 씹는 식감 — 씹어 먹는 볼 제형으로 맛이 좋고 식감이 재미있어 아이도 잘 먹음</t>
+          <t>부담 없는 가성비 — 가격 부담이 적고 식후마다 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>강한 단맛과 딱딱한 제형 — 단맛이 다소 강하고 생각보다 딱딱하여 이에 끼는 불편함이 있음</t>
+          <t>체감 효과의 미흡함 — 장기간 복용해도 체중 변화 등의 효과를 느끼기 어려움</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -5089,12 +5076,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
+          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5104,39 +5091,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910967&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=025575127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260415/rKimZ2TE65XK1Rwibsnv610910967_00_02rKimZ2TE65XK1Rwibsnv.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/VsX5iaJon2xHHTs8AQHv025575127_00_01VsX5iaJon2xHHTs8AQHv.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1493</v>
+        <v>869</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>사탕처럼 맛있는 간식 제형 — 일반 사탕처럼 달콤하고 맛이 좋아 부담 없이 즐기기 좋음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>체감되는 붓기 완화 — 붓기 관리에 도움을 주며 가성비가 훌륭함</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>믿을 만한 제조 브랜드 — 셀트리온 제조로 안심하고 꾸준히 구매함</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>딱딱한 식감과 맛의 호불호 — 캔디 제형이 다소 딱딱하고 맛에 대해 개인별 호불호가 갈림</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5144,49 +5131,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953529&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/vXg1N5D0xbSNweDPvvl2994953529_00_00vXg1N5D0xbSNweDPvvl2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>1236</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 석류 맛 — 찬물에도 잘 섞이고 맛이 좋아 부담 없이 이너뷰티를 챙기기 편함</t>
+          <t>과식 후 부담감 완화 — 많이 먹은 날 복용하여 마음에 죄책감을 줄여줌</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>높은 브랜드 신뢰도와 배송 — 대기업 브랜드 제품이라 믿을 수 있고 배송이 빠르게 완료됨</t>
+          <t>체험용 가성비 가격 — 샘플 느낌으로 부담 없이 시도하기에 적합함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>약간의 느끼함 및 당분 첨가 — 맛에서 약간의 느끼함이 느껴지거나 성분에 설탕이 포함됨</t>
+          <t>체중 감량 효과 미흡 — 복용 후 체중이 줄거나 뚜렷한 신체 변화를 느끼지 못함</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -5195,7 +5182,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5203,12 +5190,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5218,43 +5205,35 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911092&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260814/qU3FUPerTqzVYxrqf7Lx610911092_00_01qU3FUPerTqzVYxrqf7Lx.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>645</v>
+        <v>97</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>압도적인 가격 가성비 — 매우 저렴한 가격과 알찬 구성으로 부담 없이 구매할 수 있음</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>운동 전후 편리한 섭취 — 물에 가볍게 타서 마시기 편리하여 운동 보충제로 활용하기 좋음</t>
-        </is>
-      </c>
+          <t>뛰어난 가성비와 함량 — 2000mg 고함량 비타민C를 저렴한 가격에 복용 가능함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>섭취 초기 적응 필요성 — 체질에 따라 불편할 수 있어 초기 소량 테스트 복용이 필요함</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5262,12 +5241,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 스트레스 케어 올인원 15포 15일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5277,30 +5256,26 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991022&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/bpRaPOFB6GapUUiby4Vv033991022_00_00bpRaPOFB6GapUUiby4Vv.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>72</v>
+        <v>6566</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>높은 가성비 만족도 — 저렴한 가격으로 스트레스 및 피로 케어에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>하루 한 포 간편한 섭취 — 개별 포장으로 자기 전이나 피로할 때 하루 한 포씩 챙기기 편함</t>
-        </is>
-      </c>
+          <t>만족스러운 성분과 가격 — 가성비와 성분 구성에 만족하여 꾸준히 복용하기 좋음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -5309,7 +5284,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5317,12 +5292,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[보장균수 20억 CFU] 안국약품 뽀로로 유산균 요구르트맛 30포 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5332,39 +5307,43 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472881&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260828/2kboGsdLsIgwj2Bruuuv985472881_00_012kboGsdLsIgwj2Bruuuv.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>13</v>
+        <v>645</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>아이들의 높은 선호도 — 뽀로로 캐릭터 디자인과 요구르트 맛으로 아이가 거부감 없이 잘 먹음</t>
+          <t>압도적인 저렴한 가격 — 다이소 특가의 가격 경쟁력이 높고 구성이 훌륭함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>부담 없는 착한 가격 — 유명 브랜드 대비 가격 부담이 적어 데일리 유산균으로 구매하기 좋음</t>
+          <t>운동 전후 용이한 섭취 — 물에 가볍게 타서 운동 전후 보충제로 먹기 편리함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>체질별 불편감 가능성 — 크레아틴 성분 특성상 체질에 따라 복용 시 불편할 수 있음</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5372,49 +5351,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911213&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/E3CpURjLLswf9MgzRChF610911213_00_01E3CpURjLLswf9MgzRChF.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2671</v>
+        <v>46</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 데일리용 — 가격이 저렴하고 신맛이 강하지 않아 데일리용으로 섭취하기 좋음</t>
+          <t>상큼한 맛과 캔디 제형 — 사탕 형태로 상큼하고 맛있게 섭취할 수 있음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>우수한 휴대성 — 정제 타입으로 상시 휴대하며 챙겨 먹기 편함</t>
+          <t>체감되는 다리 붓기 완화 — 섭취 후 몸이나 다리의 무거운 느낌이 가벼워짐</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>명확한 효과 체감 미흡 — 함량이 상대적으로 낮아 고용량 제품 대비 확실한 효과 체감이 아쉬움</t>
+          <t>주관적인 맛 호불호 — 제품 이름에 비해서 기대보다 맛이 떨어진다는 평이 있음</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -5423,7 +5402,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5431,12 +5410,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>락피도 티니핑 빌베리스틱 12포 12일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>락피도</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5446,37 +5425,41 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=951817123&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260226/7axcAyeOWQh7bg9XboNV951817123_00_017axcAyeOWQh7bg9XboNV.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>298</v>
+        <v>3410</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>맛있는 블루베리맛 젤리 — 맛있는 블루베리 맛으로 아이와 어른 모두 젤리 대용으로 잘 먹음</t>
+          <t>눈 떨림 완화 및 수면 유도 — 눈꺼풀 떨림 증상 개선 및 수면 질 향상에 도움을 줌</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>편리한 스틱 개별 포장 — 적당한 양과 스틱 포장 형태로 하나씩 편하게 꺼내 먹기 좋음</t>
+          <t>넉넉한 소비기한과 배송 — 소비기한이 길고 배송이 빨라 이용하기 좋음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>아이 입맛에 따른 호불호 — 아이의 취향에 따라 지속적으로 잘 먹지 않는 경우가 있음</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>민감 장 복통 가스 유발 — 산화마그네슘 성분이 포함되어 장이 민감할 경우 가스나 복통 발생</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>배송 누락 사태 발생 — 주문 상품 일부가 누락되어 전달되지 않는 문제가 발생함</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
@@ -5490,49 +5473,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306208&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/wEewWmXsoUl4j1ERyFu9032306208_00_01wEewWmXsoUl4j1ERyFu9.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>616</v>
+        <v>461</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>맛있는 포도 젤리 맛 — 포도 젤리 맛 구미 제형으로 복통 없이 맛있게 간식처럼 먹기 좋음</t>
+          <t>복통 없는 장 비움 — 배 아픔 없이 섭취 후 빠른 시간 내 장을 비워 몸이 가벼워짐</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 도움 — 섭취 후 화장실을 잘 가게 도와주어 변비 완화에 효과적임</t>
+          <t>상호 시너지 효과 — 약과 음료를 함께 복용 시 배변 유도 효과가 커짐</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>개인차에 따른 배변 효과 — 젤리처럼 맛있으나 개인에 따라 변비 해소 효과 체감이 미미할 수 있음</t>
+          <t>체질에 따른 효과 차이 — 사람에 따라 반응이 적을 수 있으며 물을 충분히 섭취해야 함</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -5549,12 +5532,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 유기농 야채분말 15포 15일분</t>
+          <t>자연관 정성담은 배도라지스틱 12포</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5564,28 +5547,28 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157056&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762093&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260706/z42ScLP7B6TWURzgDPY0919157056_00_01z42ScLP7B6TWURzgDPY0.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260508/SdledEzpIdjdFFQW6W8g901762093_00_00SdledEzpIdjdFFQW6W8g.png</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>363</v>
+        <v>879</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>안심할 수 있는 국산 유기농 — 국산 유기농 야채 재료를 사용하여 안심하고 영양을 채울 수 있음</t>
+          <t>환절기 목 건강 관리 — 목감기 완화 및 기관지 보호용 스틱으로 섭취하기 좋음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>뛰어난 가격 대비 만족도 — 비싼 타사 제품과 비교해도 부족함 없는 가성비를 자랑함</t>
+          <t>우수한 가성비 — 가격 부담이 적어 자주 구매하기에 훌륭함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -5714,32 +5697,32 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -5761,52 +5744,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>종근당</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>판티오</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>안국약품</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>락피도</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>자연관</t>
         </is>
       </c>
     </row>
@@ -5818,52 +5801,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
+          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[보령약국 X Pantio] 스트레스 케어 올인원 15포 15일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[보장균수 20억 CFU] 안국약품 뽀로로 유산균 요구르트맛 30포 30일분</t>
-        </is>
-      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>락피도 티니핑 빌베리스틱 12포 12일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 유기농 야채분말 15포 15일분</t>
+          <t>자연관 정성담은 배도라지스틱 12포</t>
         </is>
       </c>
     </row>
@@ -5877,28 +5860,28 @@
         <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.7</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.7</v>
@@ -5911,34 +5894,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2184</v>
+        <v>2685</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1493</v>
+        <v>869</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>351</v>
+        <v>1236</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>6566</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>645</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="I7" s="3" t="n">
-        <v>2671</v>
+        <v>46</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>298</v>
+        <v>3410</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>616</v>
+        <v>461</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>363</v>
+        <v>879</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -5949,64 +5932,63 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>맛있고 재미있는 씹는 식감 — 씹어 먹는 볼 제형으로 맛이 좋고 식감이 재미있어 아이도 잘 먹음</t>
+          <t>부담 없는 가성비 — 가격 부담이 적고 식후마다 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>사탕처럼 맛있는 간식 제형 — 일반 사탕처럼 달콤하고 맛이 좋아 부담 없이 즐기기 좋음</t>
+          <t>체감되는 붓기 완화 — 붓기 관리에 도움을 주며 가성비가 훌륭함
+믿을 만한 제조 브랜드 — 셀트리온 제조로 안심하고 꾸준히 구매함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 석류 맛 — 찬물에도 잘 섞이고 맛이 좋아 부담 없이 이너뷰티를 챙기기 편함
-높은 브랜드 신뢰도와 배송 — 대기업 브랜드 제품이라 믿을 수 있고 배송이 빠르게 완료됨</t>
+          <t>과식 후 부담감 완화 — 많이 먹은 날 복용하여 마음에 죄책감을 줄여줌
+체험용 가성비 가격 — 샘플 느낌으로 부담 없이 시도하기에 적합함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 가격 가성비 — 매우 저렴한 가격과 알찬 구성으로 부담 없이 구매할 수 있음
-운동 전후 편리한 섭취 — 물에 가볍게 타서 마시기 편리하여 운동 보충제로 활용하기 좋음</t>
+          <t>뛰어난 가성비와 함량 — 2000mg 고함량 비타민C를 저렴한 가격에 복용 가능함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>높은 가성비 만족도 — 저렴한 가격으로 스트레스 및 피로 케어에 도움을 줌
-하루 한 포 간편한 섭취 — 개별 포장으로 자기 전이나 피로할 때 하루 한 포씩 챙기기 편함</t>
+          <t>만족스러운 성분과 가격 — 가성비와 성분 구성에 만족하여 꾸준히 복용하기 좋음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>아이들의 높은 선호도 — 뽀로로 캐릭터 디자인과 요구르트 맛으로 아이가 거부감 없이 잘 먹음
-부담 없는 착한 가격 — 유명 브랜드 대비 가격 부담이 적어 데일리 유산균으로 구매하기 좋음</t>
+          <t>압도적인 저렴한 가격 — 다이소 특가의 가격 경쟁력이 높고 구성이 훌륭함
+운동 전후 용이한 섭취 — 물에 가볍게 타서 운동 전후 보충제로 먹기 편리함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 데일리용 — 가격이 저렴하고 신맛이 강하지 않아 데일리용으로 섭취하기 좋음
-우수한 휴대성 — 정제 타입으로 상시 휴대하며 챙겨 먹기 편함</t>
+          <t>상큼한 맛과 캔디 제형 — 사탕 형태로 상큼하고 맛있게 섭취할 수 있음
+체감되는 다리 붓기 완화 — 섭취 후 몸이나 다리의 무거운 느낌이 가벼워짐</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 블루베리맛 젤리 — 맛있는 블루베리 맛으로 아이와 어른 모두 젤리 대용으로 잘 먹음
-편리한 스틱 개별 포장 — 적당한 양과 스틱 포장 형태로 하나씩 편하게 꺼내 먹기 좋음</t>
+          <t>눈 떨림 완화 및 수면 유도 — 눈꺼풀 떨림 증상 개선 및 수면 질 향상에 도움을 줌
+넉넉한 소비기한과 배송 — 소비기한이 길고 배송이 빨라 이용하기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 포도 젤리 맛 — 포도 젤리 맛 구미 제형으로 복통 없이 맛있게 간식처럼 먹기 좋음
-원활한 배변 활동 도움 — 섭취 후 화장실을 잘 가게 도와주어 변비 완화에 효과적임</t>
+          <t>복통 없는 장 비움 — 배 아픔 없이 섭취 후 빠른 시간 내 장을 비워 몸이 가벼워짐
+상호 시너지 효과 — 약과 음료를 함께 복용 시 배변 유도 효과가 커짐</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>안심할 수 있는 국산 유기농 — 국산 유기농 야채 재료를 사용하여 안심하고 영양을 채울 수 있음
-뛰어난 가격 대비 만족도 — 비싼 타사 제품과 비교해도 부족함 없는 가성비를 자랑함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>환절기 목 건강 관리 — 목감기 완화 및 기관지 보호용 스틱으로 섭취하기 좋음
+우수한 가성비 — 가격 부담이 적어 자주 구매하기에 훌륭함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -6014,39 +5996,36 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>강한 단맛과 딱딱한 제형 — 단맛이 다소 강하고 생각보다 딱딱하여 이에 끼는 불편함이 있음</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>딱딱한 식감과 맛의 호불호 — 캔디 제형이 다소 딱딱하고 맛에 대해 개인별 호불호가 갈림</t>
-        </is>
-      </c>
+          <t>체감 효과의 미흡함 — 장기간 복용해도 체중 변화 등의 효과를 느끼기 어려움</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>약간의 느끼함 및 당분 첨가 — 맛에서 약간의 느끼함이 느껴지거나 성분에 설탕이 포함됨</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>섭취 초기 적응 필요성 — 체질에 따라 불편할 수 있어 초기 소량 테스트 복용이 필요함</t>
-        </is>
-      </c>
+          <t>체중 감량 효과 미흡 — 복용 후 체중이 줄거나 뚜렷한 신체 변화를 느끼지 못함</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>체질별 불편감 가능성 — 크레아틴 성분 특성상 체질에 따라 복용 시 불편할 수 있음</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>명확한 효과 체감 미흡 — 함량이 상대적으로 낮아 고용량 제품 대비 확실한 효과 체감이 아쉬움</t>
+          <t>주관적인 맛 호불호 — 제품 이름에 비해서 기대보다 맛이 떨어진다는 평이 있음</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>아이 입맛에 따른 호불호 — 아이의 취향에 따라 지속적으로 잘 먹지 않는 경우가 있음</t>
+          <t>민감 장 복통 가스 유발 — 산화마그네슘 성분이 포함되어 장이 민감할 경우 가스나 복통 발생
+배송 누락 사태 발생 — 주문 상품 일부가 누락되어 전달되지 않는 문제가 발생함</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>개인차에 따른 배변 효과 — 젤리처럼 맛있으나 개인에 따라 변비 해소 효과 체감이 미미할 수 있음</t>
+          <t>체질에 따른 효과 차이 — 사람에 따라 반응이 적을 수 있으며 물을 충분히 섭취해야 함</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -6059,47 +6038,47 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -6283,7 +6262,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6291,34 +6270,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>칼로 컷앤리셋 28포 (14일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>칼로(Kalo)</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16,150원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263650&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026365003ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>24496</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -6330,7 +6309,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6338,27 +6317,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -6373,7 +6352,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6381,35 +6360,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225906&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022590605ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>체감 피로도의 감소 — 복용 시 아침 일어남이 가뿐해지고 피로도 차이가 체감됨</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>고용량 가루 비타민C — 알약 여럿 대신 가루형으로 고용량 비타민C 섭취에 용이함</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>다량의 수분 섭취 필요 — 결석 예방을 위해 하루 2L 이상의 물을 마셔야 함</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -6424,54 +6415,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014347ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>배 아픔 없는 원활한 배변 — 복통이나 가스 참 없이 속을 편하게 해주며 화장실을 원활히 가도록 함</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>귀여운 산리오 굿즈 증정 — 구매 시 함께 증정되는 산리오 태닝 러기지택 구성의 만족도가 높음</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 기존 복용 제품에 비해 알약 크기가 약간 크게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6479,27 +6458,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014347ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -6514,7 +6493,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6522,27 +6501,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -6557,7 +6536,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6565,54 +6544,62 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>그린몬스터</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>24,700원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000172168&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017216854ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>3189</v>
+        <v>9270</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>합리적인 가격과 높은 가성비 — 가격 부담이 적어 부담 없이 정착하여 구매하기 좋음</t>
+          <t>탁월한 붓기 라인 관리 — 자극적인 음식이나 야식 섭취 후 아침 붓기 관리에 효과적임</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>장과 질 건강 케어 균주 — 듀라벡 코팅 기술과 19종 유산균으로 장내 밸런스 유지에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>물 없이 간편한 액상 포 — 소형 포 포장으로 어디서나 물 없이 쉽게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>부담 없는 포도 맛 — 과하게 달지 않고 상큼한 포도 맛이라 먹기 편함</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>은은한 한약 풍미 잔여 — 상큼한 포도 맛 뒤에 미세한 한약 느낌이 섞여 있음</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6620,45 +6607,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 (1주일분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>38,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000142695&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5553</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>신속한 숙면 유도 효과 — 한 포 섭취 후 뒤척임 없이 빠르게 숙면에 들도록 도와줌</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>식약처 인정 식물성 원료 — 100% 식물 유래 원료를 사용하여 수면 케어 루틴으로 활용하기 좋음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0014/A00000014269532ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -6675,41 +6650,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2개월분의 넉넉한 기획 — 60캡슐 더블 기획 구성으로 두 달 동안 여유 있게 복용할 수 있음</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>캐릭터 키링 및 굿즈 증정 — 키링이나 연예인 포토카드 증정 행사로 구매 만족도가 높음</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -6718,7 +6685,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6726,45 +6693,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18,800원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>17055</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>확실한 클렌즈 및 배변 촉진 — 섭취 후 화장실을 잘 가도록 도와 더부룩함이 줄고 붓기 관리에 효과적임</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>맛있게 즐기는 젤리 제형 — 레몬, 키위, 석류 등 상큼하고 맛있는 젤리 타입으로 간편하게 먹음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -6881,52 +6836,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -6938,52 +6893,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>칼로(Kalo)</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>판도라</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>빌드</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>그린몬스터</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대원제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
         </is>
       </c>
     </row>
@@ -6995,52 +6950,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>칼로 컷앤리셋 28포 (14일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 (1주일분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7006,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
@@ -7059,15 +7014,11 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -7076,7 +7027,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6</v>
+        <v>24496</v>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
@@ -7084,17 +7035,13 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="n">
-        <v>3189</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>5553</v>
-      </c>
+        <v>9270</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="n">
-        <v>17055</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+      <c r="L7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7102,39 +7049,25 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>배 아픔 없는 원활한 배변 — 복통이나 가스 참 없이 속을 편하게 해주며 화장실을 원활히 가도록 함
-귀여운 산리오 굿즈 증정 — 구매 시 함께 증정되는 산리오 태닝 러기지택 구성의 만족도가 높음</t>
-        </is>
-      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>체감 피로도의 감소 — 복용 시 아침 일어남이 가뿐해지고 피로도 차이가 체감됨
+고용량 가루 비타민C — 알약 여럿 대신 가루형으로 고용량 비타민C 섭취에 용이함</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>합리적인 가격과 높은 가성비 — 가격 부담이 적어 부담 없이 정착하여 구매하기 좋음
-장과 질 건강 케어 균주 — 듀라벡 코팅 기술과 19종 유산균으로 장내 밸런스 유지에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>신속한 숙면 유도 효과 — 한 포 섭취 후 뒤척임 없이 빠르게 숙면에 들도록 도와줌
-식약처 인정 식물성 원료 — 100% 식물 유래 원료를 사용하여 수면 케어 루틴으로 활용하기 좋음</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>2개월분의 넉넉한 기획 — 60캡슐 더블 기획 구성으로 두 달 동안 여유 있게 복용할 수 있음
-캐릭터 키링 및 굿즈 증정 — 키링이나 연예인 포토카드 증정 행사로 구매 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>확실한 클렌즈 및 배변 촉진 — 섭취 후 화장실을 잘 가도록 도와 더부룩함이 줄고 붓기 관리에 효과적임
-맛있게 즐기는 젤리 제형 — 레몬, 키위, 석류 등 상큼하고 맛있는 젤리 타입으로 간편하게 먹음</t>
-        </is>
-      </c>
+          <t>탁월한 붓기 라인 관리 — 자극적인 음식이나 야식 섭취 후 아침 붓기 관리에 효과적임
+물 없이 간편한 액상 포 — 소형 포 포장으로 어디서나 물 없이 쉽게 섭취 가능함
+부담 없는 포도 맛 — 과하게 달지 않고 상큼한 포도 맛이라 먹기 편함</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7144,15 +7077,19 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 기존 복용 제품에 비해 알약 크기가 약간 크게 느껴짐</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>다량의 수분 섭취 필요 — 결석 예방을 위해 하루 2L 이상의 물을 마셔야 함</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>은은한 한약 풍미 잔여 — 상큼한 포도 맛 뒤에 미세한 한약 느낌이 섞여 있음</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
@@ -7165,52 +7102,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>16,150원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>18,800원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>12,900원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>24,700원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>38,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>16,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>18,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>18,900원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>31,400원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>18,800원</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7340,25 +7277,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -7368,48 +7305,48 @@
         <v>22.5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -7418,13 +7355,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7434,29 +7371,29 @@
         <v>7.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -7468,7 +7405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7484,6 +7421,50 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
